--- a/data/trans_bre/IMC_inf_MED_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R3-Estudios-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-5.373647477561463</v>
+        <v>-5.246431456068251</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-0.7767071094964995</v>
+        <v>-2.18940022515258</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-8.233717644859457</v>
+        <v>-2.346966319612714</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.1991811937856583</v>
+        <v>-0.213833174697326</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.03280283418410719</v>
+        <v>-0.1067774880346015</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.4581751578092188</v>
+        <v>-0.1305997740319442</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-17.97535676750665</v>
+        <v>-16.41566806211573</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-15.75557314891971</v>
+        <v>-14.26690366312807</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-25.5835501875296</v>
+        <v>-22.86627339138914</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.5184558172351673</v>
+        <v>-0.5419541232732161</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.5525696621685398</v>
+        <v>-0.5450957872215494</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.9202268930437877</v>
+        <v>-0.8098057276456829</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6.76095081135417</v>
+        <v>6.961686317654604</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>13.74284057484126</v>
+        <v>9.879848580333597</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>9.496853899647146</v>
+        <v>16.2402930367657</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.3438601883123997</v>
+        <v>0.377304494578921</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7992332007604307</v>
+        <v>0.6871445811020023</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.904157043877724</v>
+        <v>2.248688257235526</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-6.770950755567823</v>
+        <v>-5.020088859426683</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-10.1564155999843</v>
+        <v>-10.82032639986225</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-10.50751592464113</v>
+        <v>-9.954947945890675</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2281961190630423</v>
+        <v>-0.1826261393783351</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.4420879106225391</v>
+        <v>-0.4790115525279187</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.4461576406066076</v>
+        <v>-0.4397579599822293</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-11.93012143278682</v>
+        <v>-10.0980966971087</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-14.61665336383384</v>
+        <v>-15.08366833959695</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-17.69284269683062</v>
+        <v>-16.58602730726968</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.3700214693185538</v>
+        <v>-0.3369783849773066</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.5755086603815939</v>
+        <v>-0.5981384450599407</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.6457783796011703</v>
+        <v>-0.6332909485782121</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.5739408290238754</v>
+        <v>-0.1079903264364556</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-5.20270375548784</v>
+        <v>-6.033507611983438</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-3.095678026810964</v>
+        <v>-3.012151235726985</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.01539129442492061</v>
+        <v>-0.003506887282112463</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.2571649403589754</v>
+        <v>-0.3062353340484407</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.1532629907831277</v>
+        <v>-0.153494502004165</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-5.084557468368345</v>
+        <v>-3.709857717291842</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-1.933854515288241</v>
+        <v>0.2285693509383485</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-1.162752349252367</v>
+        <v>-0.733112236615667</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.2110611924128826</v>
+        <v>-0.1700371712854967</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.1202726511867057</v>
+        <v>0.01687804732829326</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.1113914858660418</v>
+        <v>-0.07472756096899931</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-14.44875776030286</v>
+        <v>-12.56677153902242</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-9.497722044500904</v>
+        <v>-6.771073610465852</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-9.729829668429808</v>
+        <v>-8.627622307435265</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.5049902043660826</v>
+        <v>-0.4681778833527462</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.4738292221551982</v>
+        <v>-0.3961443577033096</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.6497075503597579</v>
+        <v>-0.6368466548139946</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3.642026159779626</v>
+        <v>4.029860314811197</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5.971563998149629</v>
+        <v>6.571897498020624</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6.485873857925275</v>
+        <v>6.686634709765737</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1957688077162323</v>
+        <v>0.2303303196356366</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.5782632148889609</v>
+        <v>0.6144291008249516</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1.053011125797811</v>
+        <v>1.223182213035278</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-6.29378892230347</v>
+        <v>-4.853077299566574</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-7.554169948985562</v>
+        <v>-7.441287865984539</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-8.232768784487323</v>
+        <v>-7.260970381988314</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.2239308548973603</v>
+        <v>-0.1875514816902798</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.3517942825767651</v>
+        <v>-0.3671751801100362</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.412509963009819</v>
+        <v>-0.3788878588518601</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-10.7293796426212</v>
+        <v>-8.766958286760996</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-11.27018647300211</v>
+        <v>-10.92596402798728</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-13.6514073259646</v>
+        <v>-12.41912495603186</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.3548010914679697</v>
+        <v>-0.3185499067353299</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.4782752908541811</v>
+        <v>-0.4941096014565154</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.5911076623759354</v>
+        <v>-0.5643164332861496</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>-1.812255892675549</v>
+        <v>-0.6719581862270014</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>-3.917953806249336</v>
+        <v>-3.97515238905609</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-3.279737292338528</v>
+        <v>-2.234229144703206</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.0727105771039579</v>
+        <v>-0.02870759691275226</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1927289360695908</v>
+        <v>-0.2161469352470453</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.189527657711403</v>
+        <v>-0.1266852766338358</v>
       </c>
     </row>
     <row r="16">
